--- a/public/excels/default-members.xlsx
+++ b/public/excels/default-members.xlsx
@@ -2109,7 +2109,7 @@
       <c r="C36" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="3" t="s">
         <v>139</v>
       </c>
     </row>
@@ -2165,7 +2165,7 @@
       <c r="C40" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="3" t="s">
         <v>155</v>
       </c>
     </row>

--- a/public/excels/default-members.xlsx
+++ b/public/excels/default-members.xlsx
@@ -84,7 +84,7 @@
     <t>朱载坖</t>
   </si>
   <si>
-    <t>http://k.sinaimg.cn/n/sinacn10106/155/w640h315/20200229/5b0c-iqfqmas5532957.jpg/w700d1q75cms.jpg</t>
+    <t>./images/zhu-zaiji.png</t>
   </si>
   <si>
     <t>000003</t>
@@ -105,7 +105,7 @@
     <t>内阁</t>
   </si>
   <si>
-    <t>https://pics3.baidu.com/feed/9f510fb30f2442a78cf239bf109e4c5bd013021e.jpeg@f_auto?token=ed160534423d78057f892d2ccc1ca56f</t>
+    <t>./images/yan-song.png</t>
   </si>
   <si>
     <t>000005</t>
@@ -117,7 +117,7 @@
     <t>内阁 户部</t>
   </si>
   <si>
-    <t>./images/xu-jie.png</t>
+    <t>./images/xu-jie2.png</t>
   </si>
   <si>
     <t>000006</t>
@@ -252,7 +252,7 @@
     <t>浙江巡抚署|布政使司</t>
   </si>
   <si>
-    <t>https://5b0988e595225.cdn.sohucs.com/images/20191127/bc38c7c521b14ba2baf63c932cd48742.jpeg</t>
+    <t>./images/zheng-bichang.png</t>
   </si>
   <si>
     <t>000018</t>
@@ -264,7 +264,7 @@
     <t>浙江按察使司|布政使司</t>
   </si>
   <si>
-    <t>https://pic4.zhimg.com/v2-ba6876a60f9dc8147e5af8c603190159_r.jpg</t>
+    <t>./images/he-maocai.png</t>
   </si>
   <si>
     <t>000019</t>
@@ -276,7 +276,7 @@
     <t>司礼监</t>
   </si>
   <si>
-    <t>https://pic.rmb.bdstatic.com/bjh/events/9247bf63ce76c1566fd4a87604b4137b.jpeg@h_1280</t>
+    <t>./images/lv-fang.png</t>
   </si>
   <si>
     <t>000020</t>
@@ -285,7 +285,7 @@
     <t>陈洪</t>
   </si>
   <si>
-    <t>https://bj.bcebos.com/bjh-pixel/17074404270947698282_0_ainote_new.jpg</t>
+    <t>./images/chen-hong.png</t>
   </si>
   <si>
     <t>000021</t>
@@ -294,7 +294,7 @@
     <t>黄锦</t>
   </si>
   <si>
-    <t>https://pica.zhimg.com/v2-3aaacfb766f01fbb7af337f709683413_r.jpg?source=1def8aca</t>
+    <t>./images/huang-jin.png</t>
   </si>
   <si>
     <t>000022</t>
@@ -342,7 +342,7 @@
     <t>台州卫</t>
   </si>
   <si>
-    <t>https://p3.itc.cn/images01/20200713/e40f18569c1f47b9a6607909d0f9661a.jpeg</t>
+    <t>./images/qi-jiguang.png</t>
   </si>
   <si>
     <t>000026</t>
@@ -354,7 +354,7 @@
     <t>杭州府</t>
   </si>
   <si>
-    <t>https://pic.rmb.bdstatic.com/5fdacac31c40f7944002be17c6aa2b9b.jpeg@c_1,w_653,h_508,x_0,y_15</t>
+    <t>./images/ma-ningyuan.png</t>
   </si>
   <si>
     <t>000027</t>
@@ -390,7 +390,7 @@
     <t>北镇抚司</t>
   </si>
   <si>
-    <t>https://k.sinaimg.cn/n/sinakd10101/155/w640h315/20210622/b870-krwipar0342715.jpg/w700d1q75cms.jpg</t>
+    <t>./images/zhu-qi.png</t>
   </si>
   <si>
     <t>000030</t>
@@ -423,7 +423,7 @@
     <t>淳安县衙</t>
   </si>
   <si>
-    <t>https://pic.rmb.bdstatic.com/bjh/down/c73e2aa14974c1381b8101928dffef4b.jpeg</t>
+    <t>./images/tian-youlu.png</t>
   </si>
   <si>
     <t>000033</t>
@@ -519,7 +519,7 @@
     <t>孟公公</t>
   </si>
   <si>
-    <t>https://nimg.ws.126.net/?url=http%3A%2F%2Fdingyue.ws.126.net%2F2024%2F0207%2Fd9497187j00s8hhs601pod001kw00u8m.jpg&amp;thumbnail=660x2147483647&amp;quality=80&amp;type=jpg</t>
+    <t>./images/meng-gonggong.png</t>
   </si>
   <si>
     <t>000042</t>
@@ -576,7 +576,7 @@
     <t>倭寇海盗组织</t>
   </si>
   <si>
-    <t>https://pic1.zhimg.com/100/v2-f24f52ac6431f4cbc0e7dae9e026ddfa_r.jpg</t>
+    <t>./images/jingshang-shisilang.png</t>
   </si>
   <si>
     <t>000047</t>

--- a/public/excels/default-members.xlsx
+++ b/public/excels/default-members.xlsx
@@ -240,7 +240,7 @@
     <t>翰林院 杭州府</t>
   </si>
   <si>
-    <t>https://p5.itc.cn/images01/20210725/168e093bd60d4db9b1da751bc09869df.jpeg</t>
+    <t>./images/gao-hanwen.png</t>
   </si>
   <si>
     <t>000017</t>
@@ -555,7 +555,7 @@
     <t>裕王府</t>
   </si>
   <si>
-    <t>https://q4.itc.cn/images01/20251104/d027840e814144679999799784bf3ab2.jpeg</t>
+    <t>./images/li-cefei.png</t>
   </si>
   <si>
     <t>000045</t>

--- a/public/excels/default-members.xlsx
+++ b/public/excels/default-members.xlsx
@@ -489,7 +489,7 @@
     <t>国子监</t>
   </si>
   <si>
-    <t>https://pic.rmb.bdstatic.com/bjh/cms/240822/aba6580ce7eeff5e5e6c79efb0277f9f_1724307990.0533_419.jpeg</t>
+    <t>./images/li-qingyuan.png</t>
   </si>
   <si>
     <t>000039</t>
@@ -531,7 +531,7 @@
     <t>工部</t>
   </si>
   <si>
-    <t>https://pic.rmb.bdstatic.com/bjh/cms/240905/3669c2e74451d13d335e5068e4e5a907_1725511981.4027_581.jpeg</t>
+    <t>./images/xu-fan.png</t>
   </si>
   <si>
     <t>000043</t>

--- a/public/excels/default-members.xlsx
+++ b/public/excels/default-members.xlsx
@@ -117,7 +117,7 @@
     <t>内阁 户部</t>
   </si>
   <si>
-    <t>./images/xu-jie2.png</t>
+    <t>./images/xu-jie.png</t>
   </si>
   <si>
     <t>000006</t>

--- a/public/excels/default-members.xlsx
+++ b/public/excels/default-members.xlsx
@@ -138,7 +138,7 @@
     <t>高拱</t>
   </si>
   <si>
-    <t>https://pic.rmb.bdstatic.com/bjh/cms/251211/c9400d9481b8bef0d2089acc0dcb5d4f_1765419986.2928_769.jpeg</t>
+    <t>./images/gao-gong.png</t>
   </si>
   <si>
     <t>000008</t>
@@ -150,7 +150,7 @@
     <t>内阁 兵部</t>
   </si>
   <si>
-    <t>https://img1.baidu.com/it/u=1932781326,3970607845&amp;fm=253&amp;app=138&amp;f=JPEG?w=969&amp;h=568</t>
+    <t>./images/zhang-juzheng.png</t>
   </si>
   <si>
     <t>000009</t>
@@ -1717,7 +1717,7 @@
       <c r="C8" t="s">
         <v>26</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" t="s">
         <v>34</v>
       </c>
     </row>
@@ -1731,7 +1731,7 @@
       <c r="C9" t="s">
         <v>37</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" t="s">
         <v>38</v>
       </c>
     </row>
@@ -2298,14 +2298,12 @@
     </row>
   </sheetData>
   <hyperlinks>
-    <hyperlink ref="D9" r:id="rId1" display="https://img1.baidu.com/it/u=1932781326,3970607845&amp;fm=253&amp;app=138&amp;f=JPEG?w=969&amp;h=568"/>
-    <hyperlink ref="D8" r:id="rId2" display="https://pic.rmb.bdstatic.com/bjh/cms/251211/c9400d9481b8bef0d2089acc0dcb5d4f_1765419986.2928_769.jpeg"/>
-    <hyperlink ref="D10" r:id="rId3" display="https://pic.rmb.bdstatic.com/bjh/cms/251211/061a156c6956be94fdbf37150ef1595c_1765419986.5345_962.jpeg"/>
-    <hyperlink ref="D36" r:id="rId4" display="https://i1.hdslb.com/bfs/archive/48a28178cf3787ff65505f8271489e858e40bb61.jpg"/>
-    <hyperlink ref="D16" r:id="rId5" display="https://i0.hdslb.com/bfs/archive/df3863c962c3374e7a21544940831a4412634925.jpg@1200w_630h"/>
-    <hyperlink ref="D13" r:id="rId6" display="https://pic4.zhimg.com/v2-5826144298f140ca238949087e9c14a3_r.jpg"/>
-    <hyperlink ref="D2" r:id="rId7" display="./images/zhu-houcong.png"/>
-    <hyperlink ref="D40" r:id="rId8" display="https://bj.bcebos.com/bjh-pixel/17095232360135075178_1_ainote_new.jpg"/>
+    <hyperlink ref="D10" r:id="rId1" display="https://pic.rmb.bdstatic.com/bjh/cms/251211/061a156c6956be94fdbf37150ef1595c_1765419986.5345_962.jpeg"/>
+    <hyperlink ref="D36" r:id="rId2" display="https://i1.hdslb.com/bfs/archive/48a28178cf3787ff65505f8271489e858e40bb61.jpg"/>
+    <hyperlink ref="D16" r:id="rId3" display="https://i0.hdslb.com/bfs/archive/df3863c962c3374e7a21544940831a4412634925.jpg@1200w_630h"/>
+    <hyperlink ref="D13" r:id="rId4" display="https://pic4.zhimg.com/v2-5826144298f140ca238949087e9c14a3_r.jpg"/>
+    <hyperlink ref="D2" r:id="rId5" display="./images/zhu-houcong.png"/>
+    <hyperlink ref="D40" r:id="rId6" display="https://bj.bcebos.com/bjh-pixel/17095232360135075178_1_ainote_new.jpg"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/public/excels/default-members.xlsx
+++ b/public/excels/default-members.xlsx
@@ -36,16 +36,16 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="188">
   <si>
-    <t>employeeId</t>
-  </si>
-  <si>
-    <t>name</t>
-  </si>
-  <si>
-    <t>department</t>
-  </si>
-  <si>
-    <t>avatar</t>
+    <t>EmployeeID (工号)</t>
+  </si>
+  <si>
+    <t>Name (姓名)</t>
+  </si>
+  <si>
+    <t>Department (部门)</t>
+  </si>
+  <si>
+    <t>Avatar (头像)</t>
   </si>
   <si>
     <t>age</t>
@@ -1232,12 +1232,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
@@ -1570,9 +1573,10 @@
   <dimension ref="A1:J51"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
   <cols>
-    <col min="1" max="2" width="15" customWidth="1"/>
-    <col min="3" max="3" width="44.0909090909091" customWidth="1"/>
-    <col min="4" max="4" width="40" customWidth="1"/>
+    <col min="1" max="1" width="21" customWidth="1"/>
+    <col min="2" max="2" width="16" customWidth="1"/>
+    <col min="3" max="3" width="44.5454545454545" customWidth="1"/>
+    <col min="4" max="4" width="34.9090909090909" customWidth="1"/>
     <col min="5" max="10" width="15" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1589,27 +1593,27 @@
       <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:10">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>10</v>
       </c>
       <c r="B2" t="s">
@@ -1618,7 +1622,7 @@
       <c r="C2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" s="3" t="s">
+      <c r="D2" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E2">
@@ -1626,7 +1630,7 @@
       </c>
     </row>
     <row r="3" spans="1:10">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="6" t="s">
         <v>14</v>
       </c>
       <c r="B3" t="s">
@@ -1640,7 +1644,7 @@
       </c>
     </row>
     <row r="4" spans="1:10">
-      <c r="A4" s="5" t="s">
+      <c r="A4" s="6" t="s">
         <v>17</v>
       </c>
       <c r="B4" t="s">
@@ -1654,7 +1658,7 @@
       </c>
     </row>
     <row r="5" spans="1:10">
-      <c r="A5" s="5" t="s">
+      <c r="A5" s="6" t="s">
         <v>20</v>
       </c>
       <c r="B5" t="s">
@@ -1671,7 +1675,7 @@
       </c>
     </row>
     <row r="6" spans="1:10">
-      <c r="A6" s="5" t="s">
+      <c r="A6" s="6" t="s">
         <v>24</v>
       </c>
       <c r="B6" t="s">
@@ -1688,7 +1692,7 @@
       </c>
     </row>
     <row r="7" spans="1:10">
-      <c r="A7" s="5" t="s">
+      <c r="A7" s="6" t="s">
         <v>28</v>
       </c>
       <c r="B7" t="s">
@@ -1708,7 +1712,7 @@
       </c>
     </row>
     <row r="8" spans="1:10">
-      <c r="A8" s="5" t="s">
+      <c r="A8" s="6" t="s">
         <v>32</v>
       </c>
       <c r="B8" t="s">
@@ -1722,7 +1726,7 @@
       </c>
     </row>
     <row r="9" spans="1:10">
-      <c r="A9" s="5" t="s">
+      <c r="A9" s="6" t="s">
         <v>35</v>
       </c>
       <c r="B9" t="s">
@@ -1736,7 +1740,7 @@
       </c>
     </row>
     <row r="10" spans="1:10">
-      <c r="A10" s="5" t="s">
+      <c r="A10" s="6" t="s">
         <v>39</v>
       </c>
       <c r="B10" t="s">
@@ -1745,12 +1749,12 @@
       <c r="C10" t="s">
         <v>22</v>
       </c>
-      <c r="D10" s="3" t="s">
+      <c r="D10" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="11" spans="1:10">
-      <c r="A11" s="5" t="s">
+      <c r="A11" s="6" t="s">
         <v>42</v>
       </c>
       <c r="B11" t="s">
@@ -1764,7 +1768,7 @@
       </c>
     </row>
     <row r="12" spans="1:10">
-      <c r="A12" s="5" t="s">
+      <c r="A12" s="6" t="s">
         <v>45</v>
       </c>
       <c r="B12" t="s">
@@ -1778,7 +1782,7 @@
       </c>
     </row>
     <row r="13" spans="1:10">
-      <c r="A13" s="5" t="s">
+      <c r="A13" s="6" t="s">
         <v>49</v>
       </c>
       <c r="B13" t="s">
@@ -1787,12 +1791,12 @@
       <c r="C13" t="s">
         <v>51</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="5" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="14" spans="1:10">
-      <c r="A14" s="5" t="s">
+      <c r="A14" s="6" t="s">
         <v>53</v>
       </c>
       <c r="B14" t="s">
@@ -1806,7 +1810,7 @@
       </c>
     </row>
     <row r="15" spans="1:10">
-      <c r="A15" s="5" t="s">
+      <c r="A15" s="6" t="s">
         <v>57</v>
       </c>
       <c r="B15" t="s">
@@ -1820,7 +1824,7 @@
       </c>
     </row>
     <row r="16" spans="1:10">
-      <c r="A16" s="5" t="s">
+      <c r="A16" s="6" t="s">
         <v>61</v>
       </c>
       <c r="B16" t="s">
@@ -1829,12 +1833,12 @@
       <c r="C16" t="s">
         <v>63</v>
       </c>
-      <c r="D16" s="3" t="s">
+      <c r="D16" s="4" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="5" t="s">
+      <c r="A17" s="6" t="s">
         <v>65</v>
       </c>
       <c r="B17" t="s">
@@ -1848,7 +1852,7 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="5" t="s">
+      <c r="A18" s="6" t="s">
         <v>69</v>
       </c>
       <c r="B18" t="s">
@@ -1862,7 +1866,7 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="5" t="s">
+      <c r="A19" s="6" t="s">
         <v>73</v>
       </c>
       <c r="B19" t="s">
@@ -1876,7 +1880,7 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="5" t="s">
+      <c r="A20" s="6" t="s">
         <v>77</v>
       </c>
       <c r="B20" t="s">
@@ -1890,7 +1894,7 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="5" t="s">
+      <c r="A21" s="6" t="s">
         <v>81</v>
       </c>
       <c r="B21" t="s">
@@ -1904,7 +1908,7 @@
       </c>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="5" t="s">
+      <c r="A22" s="6" t="s">
         <v>84</v>
       </c>
       <c r="B22" t="s">
@@ -1918,7 +1922,7 @@
       </c>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="5" t="s">
+      <c r="A23" s="6" t="s">
         <v>87</v>
       </c>
       <c r="B23" t="s">
@@ -1932,7 +1936,7 @@
       </c>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="5" t="s">
+      <c r="A24" s="6" t="s">
         <v>91</v>
       </c>
       <c r="B24" t="s">
@@ -1946,7 +1950,7 @@
       </c>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="5" t="s">
+      <c r="A25" s="6" t="s">
         <v>95</v>
       </c>
       <c r="B25" t="s">
@@ -1960,7 +1964,7 @@
       </c>
     </row>
     <row r="26" spans="1:4">
-      <c r="A26" s="5" t="s">
+      <c r="A26" s="6" t="s">
         <v>99</v>
       </c>
       <c r="B26" t="s">
@@ -1974,7 +1978,7 @@
       </c>
     </row>
     <row r="27" spans="1:4">
-      <c r="A27" s="5" t="s">
+      <c r="A27" s="6" t="s">
         <v>103</v>
       </c>
       <c r="B27" t="s">
@@ -1988,7 +1992,7 @@
       </c>
     </row>
     <row r="28" spans="1:4">
-      <c r="A28" s="5" t="s">
+      <c r="A28" s="6" t="s">
         <v>107</v>
       </c>
       <c r="B28" t="s">
@@ -2002,7 +2006,7 @@
       </c>
     </row>
     <row r="29" spans="1:4">
-      <c r="A29" s="5" t="s">
+      <c r="A29" s="6" t="s">
         <v>111</v>
       </c>
       <c r="B29" t="s">
@@ -2016,7 +2020,7 @@
       </c>
     </row>
     <row r="30" spans="1:4">
-      <c r="A30" s="5" t="s">
+      <c r="A30" s="6" t="s">
         <v>115</v>
       </c>
       <c r="B30" t="s">
@@ -2030,7 +2034,7 @@
       </c>
     </row>
     <row r="31" spans="1:4">
-      <c r="A31" s="5" t="s">
+      <c r="A31" s="6" t="s">
         <v>119</v>
       </c>
       <c r="B31" t="s">
@@ -2044,7 +2048,7 @@
       </c>
     </row>
     <row r="32" spans="1:4">
-      <c r="A32" s="5" t="s">
+      <c r="A32" s="6" t="s">
         <v>122</v>
       </c>
       <c r="B32" t="s">
@@ -2058,7 +2062,7 @@
       </c>
     </row>
     <row r="33" spans="1:4">
-      <c r="A33" s="5" t="s">
+      <c r="A33" s="6" t="s">
         <v>126</v>
       </c>
       <c r="B33" t="s">
@@ -2072,7 +2076,7 @@
       </c>
     </row>
     <row r="34" spans="1:4">
-      <c r="A34" s="5" t="s">
+      <c r="A34" s="6" t="s">
         <v>130</v>
       </c>
       <c r="B34" t="s">
@@ -2086,7 +2090,7 @@
       </c>
     </row>
     <row r="35" spans="1:4">
-      <c r="A35" s="5" t="s">
+      <c r="A35" s="6" t="s">
         <v>134</v>
       </c>
       <c r="B35" t="s">
@@ -2100,7 +2104,7 @@
       </c>
     </row>
     <row r="36" spans="1:4">
-      <c r="A36" s="5" t="s">
+      <c r="A36" s="6" t="s">
         <v>137</v>
       </c>
       <c r="B36" t="s">
@@ -2109,12 +2113,12 @@
       <c r="C36" t="s">
         <v>89</v>
       </c>
-      <c r="D36" s="3" t="s">
+      <c r="D36" s="4" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:4">
-      <c r="A37" s="5" t="s">
+      <c r="A37" s="6" t="s">
         <v>140</v>
       </c>
       <c r="B37" t="s">
@@ -2128,7 +2132,7 @@
       </c>
     </row>
     <row r="38" spans="1:4">
-      <c r="A38" s="5" t="s">
+      <c r="A38" s="6" t="s">
         <v>144</v>
       </c>
       <c r="B38" t="s">
@@ -2142,7 +2146,7 @@
       </c>
     </row>
     <row r="39" spans="1:4">
-      <c r="A39" s="5" t="s">
+      <c r="A39" s="6" t="s">
         <v>148</v>
       </c>
       <c r="B39" t="s">
@@ -2156,7 +2160,7 @@
       </c>
     </row>
     <row r="40" spans="1:4">
-      <c r="A40" s="5" t="s">
+      <c r="A40" s="6" t="s">
         <v>152</v>
       </c>
       <c r="B40" t="s">
@@ -2165,12 +2169,12 @@
       <c r="C40" t="s">
         <v>154</v>
       </c>
-      <c r="D40" s="3" t="s">
+      <c r="D40" s="4" t="s">
         <v>155</v>
       </c>
     </row>
     <row r="41" spans="1:4">
-      <c r="A41" s="5" t="s">
+      <c r="A41" s="6" t="s">
         <v>156</v>
       </c>
       <c r="B41" t="s">
@@ -2184,7 +2188,7 @@
       </c>
     </row>
     <row r="42" spans="1:4">
-      <c r="A42" s="5" t="s">
+      <c r="A42" s="6" t="s">
         <v>159</v>
       </c>
       <c r="B42" t="s">
@@ -2198,7 +2202,7 @@
       </c>
     </row>
     <row r="43" spans="1:4">
-      <c r="A43" s="5" t="s">
+      <c r="A43" s="6" t="s">
         <v>162</v>
       </c>
       <c r="B43" t="s">
@@ -2212,7 +2216,7 @@
       </c>
     </row>
     <row r="44" spans="1:4">
-      <c r="A44" s="5" t="s">
+      <c r="A44" s="6" t="s">
         <v>166</v>
       </c>
       <c r="B44" t="s">
@@ -2226,7 +2230,7 @@
       </c>
     </row>
     <row r="45" spans="1:4">
-      <c r="A45" s="5" t="s">
+      <c r="A45" s="6" t="s">
         <v>170</v>
       </c>
       <c r="B45" t="s">
@@ -2240,7 +2244,7 @@
       </c>
     </row>
     <row r="46" spans="1:4">
-      <c r="A46" s="5" t="s">
+      <c r="A46" s="6" t="s">
         <v>174</v>
       </c>
       <c r="B46" t="s">
@@ -2254,7 +2258,7 @@
       </c>
     </row>
     <row r="47" spans="1:4">
-      <c r="A47" s="5" t="s">
+      <c r="A47" s="6" t="s">
         <v>177</v>
       </c>
       <c r="B47" t="s">
@@ -2268,7 +2272,7 @@
       </c>
     </row>
     <row r="48" ht="13" customHeight="1" spans="1:4">
-      <c r="A48" s="5" t="s">
+      <c r="A48" s="6" t="s">
         <v>181</v>
       </c>
       <c r="B48" t="s">
@@ -2282,17 +2286,17 @@
       </c>
     </row>
     <row r="49" spans="1:1">
-      <c r="A49" s="5" t="s">
+      <c r="A49" s="6" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="50" spans="1:1">
-      <c r="A50" s="5" t="s">
+      <c r="A50" s="6" t="s">
         <v>186</v>
       </c>
     </row>
     <row r="51" spans="1:1">
-      <c r="A51" s="5" t="s">
+      <c r="A51" s="6" t="s">
         <v>187</v>
       </c>
     </row>
